--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:30:00</t>
+          <t>2026-08-18 13:15:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:15:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-18 21:30:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2218,156 +2218,2438 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aluminium Arak</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Chadormalu SC</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-08-18 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Iran Persian Gulf Pro League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sepahan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tractor Sazi</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-08-18 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-08-18 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AGMK</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1</v>
+      </c>
+      <c r="AN15">
+        <v>-1</v>
+      </c>
+      <c r="AO15">
+        <v>-1</v>
+      </c>
+      <c r="AP15">
+        <v>-1</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mash'al</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1</v>
+      </c>
+      <c r="AN16">
+        <v>-1</v>
+      </c>
+      <c r="AO16">
+        <v>-1</v>
+      </c>
+      <c r="AP16">
+        <v>-1</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Bor</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Voždovac</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OFK Vršac</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dubočica</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jedinstvo Ub</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Grafičar</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Loznica</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Metalac GM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Borac Čačak</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Naftagas</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Teleoptik</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bačka Topola</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spartak Subotica</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Juventude</t>
         </is>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>-1</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>2026-08-18 21:35:00</t>
         </is>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU26"/>
+  <dimension ref="A1:AU29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G2">
@@ -631,68 +631,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-08-18 13:15:00</t>
+          <t>2026-08-18 08:35:00</t>
         </is>
       </c>
     </row>
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-18 13:15:00</t>
+          <t>2026-08-18 11:00:00</t>
         </is>
       </c>
     </row>
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-18 13:30:00</t>
+          <t>2026-08-18 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-18 13:30:00</t>
+          <t>2026-08-18 13:15:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-18 13:30:00</t>
+          <t>2026-08-18 13:15:00</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G11">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G12">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-08-18 14:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-08-18 19:30:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 19:30:00</t>
         </is>
       </c>
     </row>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-18 21:30:00</t>
+          <t>2026-08-18 21:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,156 +4500,645 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bačka Topola</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spartak Subotica</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Teleoptik</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Juventude</t>
         </is>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>2026-08-18 21:35:00</t>
         </is>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G12">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU29"/>
+  <dimension ref="A1:AU22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G14">
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-18 19:30:00</t>
+          <t>2026-08-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 19:30:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-08-18 21:00:00</t>
+          <t>2026-08-18 21:30:00</t>
         </is>
       </c>
     </row>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G22">
@@ -3998,1147 +3998,6 @@
         <v>0</v>
       </c>
       <c r="AU22" t="inlineStr">
-        <is>
-          <t>2026-08-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
-      <c r="AN23">
-        <v>-1</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>-1</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2026-08-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>-1</v>
-      </c>
-      <c r="AN24">
-        <v>-1</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>-1</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>2026-08-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-08-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-08-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-08-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Náutico</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>2026-08-18 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1</v>
-      </c>
-      <c r="AN29">
-        <v>-1</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>-1</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
         <is>
           <t>2026-08-18 21:35:00</t>
         </is>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.04</v>
+        <v>3.43</v>
       </c>
       <c r="O17">
-        <v>3.76</v>
+        <v>3.32</v>
       </c>
       <c r="P17">
-        <v>3.71</v>
+        <v>2.31</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="O18">
-        <v>4.28</v>
+        <v>3.76</v>
       </c>
       <c r="P18">
-        <v>5.48</v>
+        <v>3.71</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AA18">
+        <v>1.8</v>
+      </c>
+      <c r="AB18">
+        <v>1.95</v>
+      </c>
+      <c r="AC18">
+        <v>2.81</v>
+      </c>
+      <c r="AD18">
+        <v>1.4</v>
+      </c>
+      <c r="AE18">
+        <v>1.13</v>
+      </c>
+      <c r="AF18">
         <v>1.62</v>
       </c>
-      <c r="AB18">
-        <v>2.15</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.43</v>
+        <v>1.64</v>
       </c>
       <c r="O19">
-        <v>3.32</v>
+        <v>4.28</v>
       </c>
       <c r="P19">
-        <v>2.31</v>
+        <v>5.48</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA19">
+        <v>1.62</v>
+      </c>
+      <c r="AB19">
+        <v>2.15</v>
+      </c>
+      <c r="AC19">
+        <v>2.49</v>
+      </c>
+      <c r="AD19">
+        <v>1.48</v>
+      </c>
+      <c r="AE19">
+        <v>1.16</v>
+      </c>
+      <c r="AF19">
+        <v>1.57</v>
+      </c>
+      <c r="AG19">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.21</v>
+      </c>
+      <c r="AK19">
         <v>2</v>
-      </c>
-      <c r="AB19">
-        <v>1.76</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.43</v>
+        <v>1.64</v>
       </c>
       <c r="O17">
-        <v>3.32</v>
+        <v>4.28</v>
       </c>
       <c r="P17">
-        <v>2.31</v>
+        <v>5.48</v>
       </c>
       <c r="Q17">
-        <v>3.64</v>
+        <v>2.15</v>
       </c>
       <c r="R17">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>2.87</v>
+        <v>3.28</v>
       </c>
       <c r="U17">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AA17">
+        <v>1.62</v>
+      </c>
+      <c r="AB17">
+        <v>2.15</v>
+      </c>
+      <c r="AC17">
+        <v>2.49</v>
+      </c>
+      <c r="AD17">
+        <v>1.48</v>
+      </c>
+      <c r="AE17">
+        <v>1.16</v>
+      </c>
+      <c r="AF17">
+        <v>1.57</v>
+      </c>
+      <c r="AG17">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.21</v>
+      </c>
+      <c r="AK17">
         <v>2</v>
-      </c>
-      <c r="AB17">
-        <v>1.76</v>
-      </c>
-      <c r="AC17">
-        <v>3.55</v>
-      </c>
-      <c r="AD17">
-        <v>1.19</v>
-      </c>
-      <c r="AE17">
-        <v>1.06</v>
-      </c>
-      <c r="AF17">
-        <v>1.78</v>
-      </c>
-      <c r="AG17">
-        <v>1.89</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.56</v>
-      </c>
-      <c r="AK17">
-        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.64</v>
+        <v>3.43</v>
       </c>
       <c r="O19">
-        <v>4.28</v>
+        <v>3.32</v>
       </c>
       <c r="P19">
-        <v>5.48</v>
+        <v>2.31</v>
       </c>
       <c r="Q19">
-        <v>2.15</v>
+        <v>3.64</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="S19">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="Z19">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AA19">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AC19">
-        <v>2.49</v>
+        <v>3.55</v>
       </c>
       <c r="AD19">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q21">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="R21">
         <v>2.02</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U21">
         <v>2.99</v>
@@ -3762,34 +3762,34 @@
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AA21">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC21">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
+        <v>1.81</v>
+      </c>
+      <c r="AG21">
         <v>1.84</v>
-      </c>
-      <c r="AG21">
-        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q22">
         <v>3.04</v>
       </c>
       <c r="R22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S22">
         <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U22">
         <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W22">
         <v>1.03</v>
@@ -3928,19 +3928,19 @@
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z22">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AA22">
         <v>2.45</v>
       </c>
       <c r="AB22">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AC22">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AD22">
         <v>1.12</v>
@@ -3949,10 +3949,10 @@
         <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AG22">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q2">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="R2">
         <v>2.5</v>
       </c>
       <c r="S2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U2">
         <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AA2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB2">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AC2">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD2">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE2">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG2">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3575,13 +3575,13 @@
         <v>3</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="R20">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="S20">
         <v>1.44</v>
@@ -3590,7 +3590,7 @@
         <v>2.56</v>
       </c>
       <c r="U20">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V20">
         <v>1.32</v>
@@ -3608,13 +3608,13 @@
         <v>2.78</v>
       </c>
       <c r="AA20">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AB20">
         <v>1.65</v>
       </c>
       <c r="AC20">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AD20">
         <v>1.19</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
         <v>1.4</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3578,10 +3578,10 @@
         <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="S20">
         <v>1.44</v>
@@ -3599,7 +3599,7 @@
         <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
         <v>1.34</v>
@@ -3614,19 +3614,19 @@
         <v>1.65</v>
       </c>
       <c r="AC20">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AD20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
         <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O21">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R21">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S21">
         <v>1.43</v>
@@ -3753,40 +3753,40 @@
         <v>2.65</v>
       </c>
       <c r="U21">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="V21">
         <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
         <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB21">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC21">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AD21">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG21">
         <v>1.84</v>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3907,13 +3907,13 @@
         <v>3.04</v>
       </c>
       <c r="R22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S22">
         <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="U22">
         <v>3.6</v>
@@ -3928,16 +3928,16 @@
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z22">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AA22">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AB22">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AC22">
         <v>4.9</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="Q2">
         <v>2.76</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="O17">
-        <v>4.28</v>
+        <v>3.92</v>
       </c>
       <c r="P17">
-        <v>5.48</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S17">
         <v>1.29</v>
@@ -3104,40 +3104,40 @@
         <v>2.28</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
         <v>4.4</v>
       </c>
       <c r="AA17">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AC17">
         <v>2.49</v>
       </c>
       <c r="AD17">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE17">
         <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
         <v>2</v>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="Q18">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R18">
         <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V18">
         <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3279,28 +3279,28 @@
         <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>4.07</v>
+        <v>3.8</v>
       </c>
       <c r="AA18">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB18">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF18">
         <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.43</v>
+        <v>2.9</v>
       </c>
       <c r="O19">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q19">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="V19">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB19">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AD19">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
         <v>1.36</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="AA2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB2">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AC2">
         <v>1.95</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3089,10 +3089,10 @@
         <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="R17">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="S17">
         <v>1.29</v>
@@ -3101,25 +3101,25 @@
         <v>3.28</v>
       </c>
       <c r="U17">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA17">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB17">
         <v>2.24</v>
@@ -3131,13 +3131,13 @@
         <v>1.45</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
         <v>3.7</v>
@@ -3258,19 +3258,19 @@
         <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U18">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3282,25 +3282,25 @@
         <v>3.8</v>
       </c>
       <c r="AA18">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB18">
         <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE18">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
         <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,34 +3409,34 @@
         <v>2.9</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P19">
         <v>2.45</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
         <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
         <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.36</v>
@@ -3448,13 +3448,13 @@
         <v>2.02</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC19">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
         <v>1.08</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3578,7 +3578,7 @@
         <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
       <c r="R20">
         <v>1.99</v>
@@ -3587,7 +3587,7 @@
         <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
         <v>3.05</v>
@@ -3608,10 +3608,10 @@
         <v>2.78</v>
       </c>
       <c r="AA20">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AB20">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC20">
         <v>3.9</v>
@@ -3620,13 +3620,13 @@
         <v>1.22</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG20">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3747,25 +3747,25 @@
         <v>2.03</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
         <v>3.1</v>
@@ -3786,10 +3786,10 @@
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG21">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
         <v>3.16</v>
       </c>
       <c r="Q22">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="R22">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
         <v>1.5</v>
@@ -3916,7 +3916,7 @@
         <v>2.35</v>
       </c>
       <c r="U22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V22">
         <v>1.25</v>
@@ -3937,7 +3937,7 @@
         <v>2.48</v>
       </c>
       <c r="AB22">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC22">
         <v>4.9</v>
@@ -3949,10 +3949,10 @@
         <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
         <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="Q2">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="R2">
         <v>2.5</v>
       </c>
       <c r="S2">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T2">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U2">
         <v>1.99</v>
@@ -662,16 +662,16 @@
         <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.09</v>
       </c>
       <c r="Z2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA2">
         <v>1.4</v>
@@ -680,13 +680,13 @@
         <v>2.87</v>
       </c>
       <c r="AC2">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD2">
         <v>1.85</v>
       </c>
       <c r="AE2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF2">
         <v>1.34</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.61</v>
+        <v>3.48</v>
       </c>
       <c r="R20">
         <v>1.99</v>
@@ -3735,28 +3735,28 @@
         <v>2.15</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
         <v>2.83</v>
       </c>
       <c r="R21">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
         <v>1.05</v>
@@ -3765,7 +3765,7 @@
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
         <v>3.1</v>
@@ -3786,10 +3786,10 @@
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G14">
@@ -3572,16 +3572,16 @@
         <v>2.7</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R20">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S20">
         <v>1.44</v>
@@ -3590,28 +3590,28 @@
         <v>2.75</v>
       </c>
       <c r="U20">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z20">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AA20">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AB20">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC20">
         <v>3.9</v>
@@ -3620,13 +3620,13 @@
         <v>1.22</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="R21">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S21">
         <v>1.36</v>
@@ -3753,31 +3753,31 @@
         <v>2.88</v>
       </c>
       <c r="U21">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
         <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z21">
         <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB21">
         <v>1.7</v>
       </c>
       <c r="AC21">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD21">
         <v>1.23</v>
@@ -3786,10 +3786,10 @@
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>3.05</v>
       </c>
       <c r="R22">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S22">
         <v>1.5</v>
@@ -3916,43 +3916,43 @@
         <v>2.35</v>
       </c>
       <c r="U22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
         <v>1.03</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z22">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AA22">
         <v>2.48</v>
       </c>
       <c r="AB22">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AC22">
         <v>4.9</v>
       </c>
       <c r="AD22">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O2">
         <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="Q2">
         <v>2.56</v>
@@ -674,10 +674,10 @@
         <v>7</v>
       </c>
       <c r="AA2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB2">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AC2">
         <v>1.93</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O17">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P17">
         <v>4.2</v>
@@ -3092,13 +3092,13 @@
         <v>2.25</v>
       </c>
       <c r="R17">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
         <v>2.3</v>
@@ -3119,25 +3119,25 @@
         <v>4.15</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
         <v>2.24</v>
       </c>
       <c r="AC17">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AD17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE17">
         <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="P18">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q18">
         <v>2.55</v>
@@ -3258,16 +3258,16 @@
         <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
         <v>3.3</v>
       </c>
       <c r="U18">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V18">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
         <v>1.1</v>
@@ -3276,16 +3276,16 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
         <v>1.7</v>
       </c>
       <c r="AB18">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC18">
         <v>3</v>
@@ -3300,7 +3300,7 @@
         <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O19">
         <v>3.14</v>
@@ -3415,10 +3415,10 @@
         <v>2.45</v>
       </c>
       <c r="Q19">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
         <v>1.45</v>
@@ -3445,16 +3445,16 @@
         <v>2.89</v>
       </c>
       <c r="AA19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB19">
         <v>1.74</v>
       </c>
       <c r="AC19">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE19">
         <v>1.08</v>
@@ -3602,22 +3602,22 @@
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z20">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA20">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AB20">
         <v>1.72</v>
       </c>
       <c r="AC20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
         <v>1.05</v>
@@ -3642,7 +3642,7 @@
         <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>2.05</v>
       </c>
       <c r="O21">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P21">
         <v>3.5</v>
@@ -3771,7 +3771,7 @@
         <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB21">
         <v>1.7</v>
@@ -3789,7 +3789,7 @@
         <v>1.82</v>
       </c>
       <c r="AG21">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>3.16</v>
       </c>
       <c r="Q22">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
         <v>1.95</v>
@@ -3922,13 +3922,13 @@
         <v>1.22</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z22">
         <v>2.35</v>
@@ -3937,7 +3937,7 @@
         <v>2.48</v>
       </c>
       <c r="AB22">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC22">
         <v>4.9</v>
@@ -3946,13 +3946,13 @@
         <v>1.1</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK22">
         <v>1.55</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O2">
         <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q2">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="R2">
         <v>2.5</v>
@@ -656,13 +656,13 @@
         <v>4</v>
       </c>
       <c r="U2">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -671,13 +671,13 @@
         <v>1.09</v>
       </c>
       <c r="Z2">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AA2">
         <v>1.36</v>
       </c>
       <c r="AB2">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AC2">
         <v>1.93</v>
@@ -689,10 +689,10 @@
         <v>1.33</v>
       </c>
       <c r="AF2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG2">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
         <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
         <v>2.53</v>
@@ -656,13 +656,13 @@
         <v>4</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -680,19 +680,19 @@
         <v>2.74</v>
       </c>
       <c r="AC2">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD2">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG2">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3083,34 +3083,34 @@
         <v>1.75</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
         <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
         <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.2</v>
@@ -3119,25 +3119,25 @@
         <v>4.15</v>
       </c>
       <c r="AA17">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB17">
         <v>2.24</v>
       </c>
       <c r="AC17">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="AD17">
         <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,37 +3243,37 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="Q18">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
         <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.22</v>
@@ -3282,25 +3282,25 @@
         <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
         <v>2.08</v>
       </c>
       <c r="AC18">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD18">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
         <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG18">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,58 +3406,58 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="P19">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q19">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
         <v>2.56</v>
       </c>
       <c r="U19">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
         <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z19">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AA19">
         <v>2</v>
       </c>
       <c r="AB19">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AD19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
         <v>1.83</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P20">
         <v>2.55</v>
@@ -3584,49 +3584,49 @@
         <v>1.97</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U20">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z20">
         <v>3.05</v>
       </c>
       <c r="AA20">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AB20">
         <v>1.72</v>
       </c>
       <c r="AC20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD20">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE20">
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG20">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O21">
         <v>3</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R21">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="T21">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="U21">
         <v>3.2</v>
@@ -3759,37 +3759,37 @@
         <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA21">
         <v>2.1</v>
       </c>
       <c r="AB21">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC21">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.37</v>
       </c>
       <c r="AK21">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>3.16</v>
       </c>
       <c r="Q22">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S22">
         <v>1.5</v>
@@ -3928,31 +3928,31 @@
         <v>1.06</v>
       </c>
       <c r="Y22">
+        <v>1.53</v>
+      </c>
+      <c r="Z22">
+        <v>2.4</v>
+      </c>
+      <c r="AA22">
+        <v>2.5</v>
+      </c>
+      <c r="AB22">
         <v>1.47</v>
       </c>
-      <c r="Z22">
-        <v>2.35</v>
-      </c>
-      <c r="AA22">
-        <v>2.48</v>
-      </c>
-      <c r="AB22">
-        <v>1.46</v>
-      </c>
       <c r="AC22">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD22">
         <v>1.1</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AK22">
         <v>1.55</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3572,16 +3572,16 @@
         <v>2.6</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
         <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R20">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S20">
         <v>1.4</v>
@@ -3735,22 +3735,22 @@
         <v>2.1</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R21">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T21">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U21">
         <v>3.2</v>
@@ -3765,10 +3765,10 @@
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z21">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA21">
         <v>2.1</v>
@@ -3789,7 +3789,7 @@
         <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.37</v>
       </c>
       <c r="AK21">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2">
@@ -644,7 +644,7 @@
         <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="R2">
         <v>2.5</v>
@@ -659,7 +659,7 @@
         <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="W2">
         <v>1.19</v>
@@ -671,7 +671,7 @@
         <v>1.09</v>
       </c>
       <c r="Z2">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA2">
         <v>1.36</v>
@@ -680,19 +680,19 @@
         <v>2.74</v>
       </c>
       <c r="AC2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD2">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF2">
         <v>1.34</v>
       </c>
       <c r="AG2">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
         <v>2.6</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P20">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
         <v>3.42</v>
@@ -3587,10 +3587,10 @@
         <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
         <v>1.36</v>
@@ -3738,7 +3738,7 @@
         <v>2.9</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -3786,7 +3786,7 @@
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
         <v>1.9</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O5">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="P5">
         <v>2.62</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -677,13 +677,13 @@
         <v>1.36</v>
       </c>
       <c r="AB2">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AC2">
         <v>1.93</v>
       </c>
       <c r="AD2">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AE2">
         <v>1.33</v>
@@ -3095,16 +3095,16 @@
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
         <v>1.12</v>
@@ -3116,7 +3116,7 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA17">
         <v>1.64</v>
@@ -3125,7 +3125,7 @@
         <v>2.24</v>
       </c>
       <c r="AC17">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD17">
         <v>1.46</v>
@@ -3137,7 +3137,7 @@
         <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="U18">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
         <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z18">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA18">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB18">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AC18">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="O19">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="Q19">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="R19">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
+        <v>1.33</v>
+      </c>
+      <c r="T19">
+        <v>3.4</v>
+      </c>
+      <c r="U19">
+        <v>2.35</v>
+      </c>
+      <c r="V19">
+        <v>1.51</v>
+      </c>
+      <c r="W19">
+        <v>1.1</v>
+      </c>
+      <c r="X19">
+        <v>1.04</v>
+      </c>
+      <c r="Y19">
+        <v>1.22</v>
+      </c>
+      <c r="Z19">
+        <v>3.9</v>
+      </c>
+      <c r="AA19">
+        <v>1.75</v>
+      </c>
+      <c r="AB19">
+        <v>2.08</v>
+      </c>
+      <c r="AC19">
+        <v>2.81</v>
+      </c>
+      <c r="AD19">
         <v>1.38</v>
       </c>
-      <c r="T19">
-        <v>2.56</v>
-      </c>
-      <c r="U19">
-        <v>2.8</v>
-      </c>
-      <c r="V19">
-        <v>1.32</v>
-      </c>
-      <c r="W19">
-        <v>1.06</v>
-      </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
-      <c r="Y19">
-        <v>1.38</v>
-      </c>
-      <c r="Z19">
-        <v>2.74</v>
-      </c>
-      <c r="AA19">
-        <v>2</v>
-      </c>
-      <c r="AB19">
-        <v>1.68</v>
-      </c>
-      <c r="AC19">
-        <v>3.8</v>
-      </c>
-      <c r="AD19">
-        <v>1.2</v>
-      </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R20">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
         <v>1.4</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>2.9</v>
       </c>
       <c r="P21">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
         <v>1.85</v>
@@ -3753,10 +3753,10 @@
         <v>2.39</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
         <v>1.03</v>
@@ -3789,7 +3789,7 @@
         <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.37</v>
       </c>
       <c r="AK21">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3928,10 +3928,10 @@
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z22">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA22">
         <v>2.5</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3098,7 +3098,7 @@
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
         <v>2.3</v>
@@ -3125,7 +3125,7 @@
         <v>2.24</v>
       </c>
       <c r="AC17">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD17">
         <v>1.46</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.4</v>
@@ -3267,7 +3267,7 @@
         <v>2.8</v>
       </c>
       <c r="V18">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
         <v>1.06</v>
@@ -3294,7 +3294,7 @@
         <v>1.2</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
         <v>1.83</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O19">
         <v>3.6</v>
       </c>
       <c r="P19">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q19">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="R19">
         <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
         <v>3.4</v>
       </c>
       <c r="U19">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
         <v>1.51</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.04</v>
@@ -3445,13 +3445,13 @@
         <v>3.9</v>
       </c>
       <c r="AA19">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB19">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AD19">
         <v>1.38</v>
@@ -3460,10 +3460,10 @@
         <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA3">
         <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="O5">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W5">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,22 +1296,22 @@
         <v>1.67</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1320,31 +1320,31 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P15">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
         <v>3.05</v>
@@ -3578,19 +3578,19 @@
         <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="U20">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
         <v>1.36</v>
@@ -3599,34 +3599,34 @@
         <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.33</v>
       </c>
       <c r="Z20">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA20">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG20">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,46 +3732,46 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="O21">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q21">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R21">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="S21">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T21">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="U21">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
         <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="AA21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB21">
         <v>1.68</v>
@@ -3780,16 +3780,16 @@
         <v>3.9</v>
       </c>
       <c r="AD21">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,16 +3904,16 @@
         <v>3.16</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R22">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="S22">
         <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U22">
         <v>3.6</v>
@@ -3922,34 +3922,34 @@
         <v>1.22</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z22">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AA22">
         <v>2.5</v>
       </c>
       <c r="AB22">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC22">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AD22">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG22">
         <v>1.67</v>
@@ -3968,7 +3968,7 @@
         <v>1.37</v>
       </c>
       <c r="AK22">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Q2">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S2">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V2">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W2">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z2">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA2">
         <v>1.36</v>
       </c>
       <c r="AB2">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AC2">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE2">
         <v>1.33</v>
       </c>
       <c r="AF2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
       </c>
       <c r="R17">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3116,28 +3116,28 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA17">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB17">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
         <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG17">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
         <v>3.3</v>
@@ -3252,55 +3252,55 @@
         <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="R18">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.87</v>
+        <v>2.51</v>
       </c>
       <c r="U18">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V18">
         <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y18">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA18">
         <v>2</v>
       </c>
       <c r="AB18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC18">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK18">
         <v>1.36</v>
@@ -3406,61 +3406,61 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="R19">
         <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC19">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD19">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
         <v>2.2</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
         <v>3.35</v>
@@ -3602,7 +3602,7 @@
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z20">
         <v>2.92</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="O21">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P21">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="Q21">
         <v>2.8</v>
@@ -3910,10 +3910,10 @@
         <v>1.81</v>
       </c>
       <c r="S22">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T22">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U22">
         <v>3.6</v>
@@ -3922,7 +3922,7 @@
         <v>1.22</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.06</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
         <v>2.87</v>
       </c>
       <c r="P5">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R5">
         <v>1.84</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O15">
         <v>2.8</v>
@@ -2926,55 +2926,55 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q17">
-        <v>2.15</v>
+        <v>3.29</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
+        <v>2.51</v>
+      </c>
+      <c r="U17">
+        <v>2.86</v>
+      </c>
+      <c r="V17">
+        <v>1.35</v>
+      </c>
+      <c r="W17">
+        <v>1.01</v>
+      </c>
+      <c r="X17">
+        <v>1.07</v>
+      </c>
+      <c r="Y17">
+        <v>1.33</v>
+      </c>
+      <c r="Z17">
+        <v>2.83</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AB17">
+        <v>1.62</v>
+      </c>
+      <c r="AC17">
         <v>3.5</v>
       </c>
-      <c r="U17">
-        <v>2.34</v>
-      </c>
-      <c r="V17">
-        <v>1.53</v>
-      </c>
-      <c r="W17">
-        <v>1.13</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>1.2</v>
-      </c>
-      <c r="Z17">
-        <v>4.15</v>
-      </c>
-      <c r="AA17">
-        <v>1.58</v>
-      </c>
-      <c r="AB17">
-        <v>2.2</v>
-      </c>
-      <c r="AC17">
-        <v>2.7</v>
-      </c>
       <c r="AD17">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK17">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>3.29</v>
+        <v>2.39</v>
       </c>
       <c r="R18">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z18">
-        <v>2.83</v>
+        <v>4.33</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AC18">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG18">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q19">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
         <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA19">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB19">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD19">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -1145,13 +1145,13 @@
         <v>2.24</v>
       </c>
       <c r="U5">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V5">
         <v>1.21</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
         <v>1.07</v>
@@ -1175,7 +1175,7 @@
         <v>1.1</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
         <v>2.1</v>
@@ -2757,22 +2757,22 @@
         <v>3.1</v>
       </c>
       <c r="O15">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q15">
-        <v>4.05</v>
+        <v>4.28</v>
       </c>
       <c r="R15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S15">
         <v>1.62</v>
       </c>
       <c r="T15">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="U15">
         <v>4.1</v>
@@ -2784,7 +2784,7 @@
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y15">
         <v>1.65</v>
@@ -2793,10 +2793,10 @@
         <v>2.15</v>
       </c>
       <c r="AA15">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AB15">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC15">
         <v>6.3</v>
@@ -2926,55 +2926,55 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P2">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q2">
         <v>2.23</v>
@@ -653,13 +653,13 @@
         <v>1.18</v>
       </c>
       <c r="T2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="U2">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W2">
         <v>1.22</v>
@@ -671,7 +671,7 @@
         <v>1.08</v>
       </c>
       <c r="Z2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA2">
         <v>1.36</v>
@@ -680,16 +680,16 @@
         <v>3.1</v>
       </c>
       <c r="AC2">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD2">
         <v>1.8</v>
       </c>
       <c r="AE2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG2">
         <v>3</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
         <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
+        <v>1.83</v>
+      </c>
+      <c r="O13">
+        <v>3.4</v>
+      </c>
+      <c r="P13">
+        <v>3.6</v>
+      </c>
+      <c r="Q13">
+        <v>2.28</v>
+      </c>
+      <c r="R13">
+        <v>2.25</v>
+      </c>
+      <c r="S13">
+        <v>1.3</v>
+      </c>
+      <c r="T13">
         <v>3.1</v>
       </c>
-      <c r="O13">
-        <v>3.11</v>
-      </c>
-      <c r="P13">
-        <v>2.24</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P14">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q14">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>2.86</v>
+        <v>2.97</v>
       </c>
       <c r="U14">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="AA14">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC14">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AD14">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="Q17">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="R17">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S17">
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V17">
         <v>1.35</v>
@@ -3110,34 +3110,34 @@
         <v>1.01</v>
       </c>
       <c r="X17">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z17">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AB17">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC17">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG17">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q18">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S18">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U18">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
         <v>1.53</v>
@@ -3276,19 +3276,19 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AA18">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB18">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC18">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD18">
         <v>1.37</v>
@@ -3316,7 +3316,7 @@
         <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="O19">
         <v>3.8</v>
       </c>
       <c r="P19">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
         <v>2.15</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
         <v>1.3</v>
@@ -3427,43 +3427,43 @@
         <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W19">
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA19">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
         <v>1.58</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,58 +3575,58 @@
         <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
         <v>3.35</v>
       </c>
       <c r="R20">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T20">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V20">
+        <v>1.31</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.05</v>
+      </c>
+      <c r="Y20">
         <v>1.36</v>
       </c>
-      <c r="W20">
-        <v>1.04</v>
-      </c>
-      <c r="X20">
-        <v>1.03</v>
-      </c>
-      <c r="Y20">
-        <v>1.31</v>
-      </c>
       <c r="Z20">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC20">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="AD20">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P21">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
         <v>2.8</v>
       </c>
       <c r="R21">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S21">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U21">
         <v>2.91</v>
@@ -3768,7 +3768,7 @@
         <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="AA21">
         <v>2.15</v>
@@ -3777,16 +3777,16 @@
         <v>1.68</v>
       </c>
       <c r="AC21">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
         <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
         <v>1.87</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
         <v>1.62</v>
@@ -3907,7 +3907,7 @@
         <v>3.13</v>
       </c>
       <c r="R22">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="S22">
         <v>1.53</v>
@@ -3928,16 +3928,16 @@
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="Z22">
         <v>2.31</v>
       </c>
       <c r="AA22">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB22">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC22">
         <v>5.05</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -638,61 +638,61 @@
         <v>2.05</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
         <v>3</v>
       </c>
       <c r="Q2">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="S2">
         <v>1.18</v>
       </c>
       <c r="T2">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="U2">
         <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="W2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC2">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AD2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="O3">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
         <v>1.36</v>
       </c>
       <c r="T3">
+        <v>2.8</v>
+      </c>
+      <c r="U3">
         <v>2.88</v>
       </c>
-      <c r="U3">
-        <v>2.62</v>
-      </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
+        <v>1.69</v>
+      </c>
+      <c r="AC3">
+        <v>3.5</v>
+      </c>
+      <c r="AD3">
+        <v>1.22</v>
+      </c>
+      <c r="AE3">
+        <v>1.04</v>
+      </c>
+      <c r="AF3">
         <v>1.82</v>
       </c>
-      <c r="AC3">
-        <v>3.4</v>
-      </c>
-      <c r="AD3">
-        <v>1.3</v>
-      </c>
-      <c r="AE3">
-        <v>1.07</v>
-      </c>
-      <c r="AF3">
+      <c r="AG3">
+        <v>1.82</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.26</v>
+      </c>
+      <c r="AK3">
         <v>1.73</v>
-      </c>
-      <c r="AG3">
-        <v>1.92</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.3</v>
-      </c>
-      <c r="AK3">
-        <v>1.75</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.22</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="Q4">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
+        <v>2.8</v>
+      </c>
+      <c r="U4">
         <v>2.75</v>
       </c>
-      <c r="U4">
-        <v>2.71</v>
-      </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.25</v>
+      </c>
+      <c r="Z4">
+        <v>3.38</v>
+      </c>
+      <c r="AA4">
+        <v>1.86</v>
+      </c>
+      <c r="AB4">
+        <v>1.91</v>
+      </c>
+      <c r="AC4">
+        <v>2.88</v>
+      </c>
+      <c r="AD4">
         <v>1.36</v>
       </c>
-      <c r="Z4">
-        <v>3.1</v>
-      </c>
-      <c r="AA4">
-        <v>1.88</v>
-      </c>
-      <c r="AB4">
-        <v>1.86</v>
-      </c>
-      <c r="AC4">
-        <v>4.1</v>
-      </c>
-      <c r="AD4">
-        <v>1.3</v>
-      </c>
       <c r="AE4">
+        <v>1.09</v>
+      </c>
+      <c r="AF4">
+        <v>1.84</v>
+      </c>
+      <c r="AG4">
+        <v>1.83</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.18</v>
+      </c>
+      <c r="AK4">
         <v>1.08</v>
-      </c>
-      <c r="AF4">
-        <v>1.88</v>
-      </c>
-      <c r="AG4">
-        <v>1.75</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.25</v>
-      </c>
-      <c r="AK4">
-        <v>1.07</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1130,7 +1130,7 @@
         <v>2.87</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="Q5">
         <v>3.28</v>
@@ -1154,7 +1154,7 @@
         <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y5">
         <v>1.55</v>
@@ -1163,7 +1163,7 @@
         <v>2.29</v>
       </c>
       <c r="AA5">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB5">
         <v>1.42</v>
@@ -1181,7 +1181,7 @@
         <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK5">
         <v>1.41</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-18 13:15:00</t>
+          <t>2026-08-18 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q6">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="R6">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="S6">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T6">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="U6">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="V6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Z6">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AA6">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AB6">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC6">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AD6">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AG6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AK6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-18 13:15:00</t>
+          <t>2026-08-18 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-18 13:30:00</t>
+          <t>2026-08-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q12">
-        <v>2.71</v>
+        <v>3.88</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
+        <v>1.39</v>
+      </c>
+      <c r="T12">
+        <v>2.63</v>
+      </c>
+      <c r="U12">
+        <v>2.8</v>
+      </c>
+      <c r="V12">
+        <v>1.34</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
         <v>1.33</v>
       </c>
-      <c r="T12">
-        <v>2.86</v>
-      </c>
-      <c r="U12">
-        <v>2.71</v>
-      </c>
-      <c r="V12">
-        <v>1.37</v>
-      </c>
-      <c r="W12">
-        <v>1.07</v>
-      </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.23</v>
-      </c>
       <c r="Z12">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="AA12">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC12">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG12">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15">
+        <v>3.3</v>
+      </c>
+      <c r="P15">
         <v>3.1</v>
       </c>
-      <c r="O15">
-        <v>2.7</v>
-      </c>
-      <c r="P15">
-        <v>2.37</v>
-      </c>
       <c r="Q15">
-        <v>4.28</v>
+        <v>2.71</v>
       </c>
       <c r="R15">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="S15">
+        <v>1.33</v>
+      </c>
+      <c r="T15">
+        <v>2.86</v>
+      </c>
+      <c r="U15">
+        <v>2.71</v>
+      </c>
+      <c r="V15">
+        <v>1.37</v>
+      </c>
+      <c r="W15">
+        <v>1.07</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.23</v>
+      </c>
+      <c r="Z15">
+        <v>3.42</v>
+      </c>
+      <c r="AA15">
+        <v>1.84</v>
+      </c>
+      <c r="AB15">
+        <v>1.85</v>
+      </c>
+      <c r="AC15">
+        <v>3.25</v>
+      </c>
+      <c r="AD15">
+        <v>1.28</v>
+      </c>
+      <c r="AE15">
+        <v>1.06</v>
+      </c>
+      <c r="AF15">
+        <v>1.67</v>
+      </c>
+      <c r="AG15">
+        <v>2.01</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.25</v>
+      </c>
+      <c r="AK15">
         <v>1.62</v>
-      </c>
-      <c r="T15">
-        <v>2.15</v>
-      </c>
-      <c r="U15">
-        <v>4.1</v>
-      </c>
-      <c r="V15">
-        <v>1.16</v>
-      </c>
-      <c r="W15">
-        <v>1.03</v>
-      </c>
-      <c r="X15">
-        <v>1.12</v>
-      </c>
-      <c r="Y15">
-        <v>1.65</v>
-      </c>
-      <c r="Z15">
-        <v>2.15</v>
-      </c>
-      <c r="AA15">
-        <v>2.95</v>
-      </c>
-      <c r="AB15">
-        <v>1.36</v>
-      </c>
-      <c r="AC15">
-        <v>6.3</v>
-      </c>
-      <c r="AD15">
-        <v>1.06</v>
-      </c>
-      <c r="AE15">
-        <v>1.02</v>
-      </c>
-      <c r="AF15">
-        <v>2.38</v>
-      </c>
-      <c r="AG15">
-        <v>1.5</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.33</v>
-      </c>
-      <c r="AK15">
-        <v>1.28</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="R16">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S16">
         <v>1.66</v>
@@ -2953,7 +2953,7 @@
         <v>1.58</v>
       </c>
       <c r="Z16">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA16">
         <v>2.74</v>
@@ -2968,7 +2968,7 @@
         <v>1.08</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
         <v>2.19</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-18 14:00:00</t>
+          <t>2026-08-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
+        <v>1.69</v>
+      </c>
+      <c r="O18">
+        <v>3.8</v>
+      </c>
+      <c r="P18">
+        <v>4.5</v>
+      </c>
+      <c r="Q18">
+        <v>2.15</v>
+      </c>
+      <c r="R18">
+        <v>2.4</v>
+      </c>
+      <c r="S18">
+        <v>1.3</v>
+      </c>
+      <c r="T18">
+        <v>3.5</v>
+      </c>
+      <c r="U18">
+        <v>2.3</v>
+      </c>
+      <c r="V18">
+        <v>1.55</v>
+      </c>
+      <c r="W18">
+        <v>1.13</v>
+      </c>
+      <c r="X18">
+        <v>1.03</v>
+      </c>
+      <c r="Y18">
+        <v>1.2</v>
+      </c>
+      <c r="Z18">
+        <v>4.3</v>
+      </c>
+      <c r="AA18">
+        <v>1.61</v>
+      </c>
+      <c r="AB18">
+        <v>2.25</v>
+      </c>
+      <c r="AC18">
+        <v>2.58</v>
+      </c>
+      <c r="AD18">
+        <v>1.47</v>
+      </c>
+      <c r="AE18">
+        <v>1.2</v>
+      </c>
+      <c r="AF18">
+        <v>1.58</v>
+      </c>
+      <c r="AG18">
+        <v>2.16</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.2</v>
+      </c>
+      <c r="AK18">
         <v>2.05</v>
-      </c>
-      <c r="O18">
-        <v>3.6</v>
-      </c>
-      <c r="P18">
-        <v>3.4</v>
-      </c>
-      <c r="Q18">
-        <v>2.57</v>
-      </c>
-      <c r="R18">
-        <v>2.19</v>
-      </c>
-      <c r="S18">
-        <v>1.28</v>
-      </c>
-      <c r="T18">
-        <v>3.15</v>
-      </c>
-      <c r="U18">
-        <v>2.4</v>
-      </c>
-      <c r="V18">
-        <v>1.53</v>
-      </c>
-      <c r="W18">
-        <v>1.09</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.22</v>
-      </c>
-      <c r="Z18">
-        <v>4.05</v>
-      </c>
-      <c r="AA18">
-        <v>1.7</v>
-      </c>
-      <c r="AB18">
-        <v>2.13</v>
-      </c>
-      <c r="AC18">
-        <v>2.75</v>
-      </c>
-      <c r="AD18">
-        <v>1.37</v>
-      </c>
-      <c r="AE18">
-        <v>1.12</v>
-      </c>
-      <c r="AF18">
-        <v>1.6</v>
-      </c>
-      <c r="AG18">
-        <v>2.2</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.29</v>
-      </c>
-      <c r="AK18">
-        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q19">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="R19">
+        <v>2.19</v>
+      </c>
+      <c r="S19">
+        <v>1.28</v>
+      </c>
+      <c r="T19">
+        <v>3.15</v>
+      </c>
+      <c r="U19">
         <v>2.4</v>
       </c>
-      <c r="S19">
-        <v>1.3</v>
-      </c>
-      <c r="T19">
-        <v>3.5</v>
-      </c>
-      <c r="U19">
-        <v>2.3</v>
-      </c>
       <c r="V19">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA19">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB19">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AC19">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="AD19">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.79</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>3.28</v>
+        <v>5.8</v>
       </c>
       <c r="R5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U5">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="Z5">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AA5">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AB5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AC5">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AD5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF5">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AG5">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.33</v>
+        <v>1.89</v>
       </c>
       <c r="AK5">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="P6">
-        <v>1.7</v>
+        <v>2.79</v>
       </c>
       <c r="Q6">
-        <v>5.8</v>
+        <v>3.28</v>
       </c>
       <c r="R6">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S6">
+        <v>1.57</v>
+      </c>
+      <c r="T6">
+        <v>2.24</v>
+      </c>
+      <c r="U6">
+        <v>3.58</v>
+      </c>
+      <c r="V6">
+        <v>1.21</v>
+      </c>
+      <c r="W6">
+        <v>1.04</v>
+      </c>
+      <c r="X6">
+        <v>1.1</v>
+      </c>
+      <c r="Y6">
         <v>1.55</v>
       </c>
-      <c r="T6">
-        <v>2.28</v>
-      </c>
-      <c r="U6">
-        <v>3.5</v>
-      </c>
-      <c r="V6">
-        <v>1.22</v>
-      </c>
-      <c r="W6">
-        <v>1.01</v>
-      </c>
-      <c r="X6">
-        <v>1.05</v>
-      </c>
-      <c r="Y6">
-        <v>1.49</v>
-      </c>
       <c r="Z6">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AA6">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AB6">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AC6">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="AD6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AG6">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.89</v>
+        <v>1.33</v>
       </c>
       <c r="AK6">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -615,51 +615,51 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="R2">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S2">
         <v>1.18</v>
       </c>
       <c r="T2">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="V2">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="W2">
         <v>1.2</v>
@@ -668,31 +668,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z2">
-        <v>7</v>
+        <v>6.78</v>
       </c>
       <c r="AA2">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AB2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AC2">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AD2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE2">
         <v>1.33</v>
       </c>
       <c r="AF2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AG2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -701,11 +701,11 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "73", "86"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
         <v>1.67</v>
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,42 +775,42 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3.93</v>
+        <v>3.7</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
       </c>
       <c r="R3">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S3">
         <v>1.36</v>
@@ -828,77 +828,77 @@
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB3">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
         <v>3.5</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "75"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         <v>3.75</v>
       </c>
       <c r="P4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q4">
         <v>5</v>
       </c>
       <c r="R4">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
         <v>1.36</v>
@@ -982,43 +982,43 @@
         <v>2.8</v>
       </c>
       <c r="U4">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="AA4">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
+        <v>1.94</v>
+      </c>
+      <c r="AC4">
+        <v>3.1</v>
+      </c>
+      <c r="AD4">
+        <v>1.35</v>
+      </c>
+      <c r="AE4">
+        <v>1.1</v>
+      </c>
+      <c r="AF4">
+        <v>1.83</v>
+      </c>
+      <c r="AG4">
         <v>1.91</v>
-      </c>
-      <c r="AC4">
-        <v>2.88</v>
-      </c>
-      <c r="AD4">
-        <v>1.36</v>
-      </c>
-      <c r="AE4">
-        <v>1.09</v>
-      </c>
-      <c r="AF4">
-        <v>1.84</v>
-      </c>
-      <c r="AG4">
-        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="S5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U5">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
         <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z5">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AA5">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AB5">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC5">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AD5">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE5">
         <v>1</v>
       </c>
       <c r="AF5">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG5">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
         <v>1.11</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O6">
         <v>2.87</v>
       </c>
       <c r="P6">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q6">
         <v>3.28</v>
@@ -1317,7 +1317,7 @@
         <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
         <v>1.55</v>
@@ -1326,10 +1326,10 @@
         <v>2.29</v>
       </c>
       <c r="AA6">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AB6">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AC6">
         <v>5.15</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK6">
         <v>1.41</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O7">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P7">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>4.28</v>
+        <v>3.9</v>
       </c>
       <c r="R7">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="S7">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T7">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="U7">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="V7">
         <v>1.16</v>
@@ -1480,22 +1480,22 @@
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y7">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Z7">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AA7">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AB7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC7">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="AD7">
         <v>1.06</v>
@@ -1504,10 +1504,10 @@
         <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AK7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P16">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
         <v>3.7</v>
@@ -2947,13 +2947,13 @@
         <v>1.04</v>
       </c>
       <c r="X16">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y16">
         <v>1.58</v>
       </c>
       <c r="Z16">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AA16">
         <v>2.74</v>
@@ -2974,7 +2974,7 @@
         <v>2.19</v>
       </c>
       <c r="AG16">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "46", "75", "90+4"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+4"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1116,11 +1116,11 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1581,139 +1581,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>["1", "76"]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,139 +1744,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "71"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "14", "45+2", "46", "57", "89"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1907,97 +1907,97 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="O10">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="Q10">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="S10">
+        <v>1.4</v>
+      </c>
+      <c r="T10">
+        <v>2.79</v>
+      </c>
+      <c r="U10">
+        <v>2.9</v>
+      </c>
+      <c r="V10">
+        <v>1.38</v>
+      </c>
+      <c r="W10">
+        <v>1.07</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
         <v>1.31</v>
       </c>
-      <c r="T10">
-        <v>2.97</v>
-      </c>
-      <c r="U10">
-        <v>2.58</v>
-      </c>
-      <c r="V10">
-        <v>1.4</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>1.21</v>
-      </c>
       <c r="Z10">
-        <v>3.58</v>
+        <v>3.29</v>
       </c>
       <c r="AA10">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
+        <v>1.59</v>
+      </c>
+      <c r="AC10">
+        <v>2.75</v>
+      </c>
+      <c r="AD10">
+        <v>1.2</v>
+      </c>
+      <c r="AE10">
+        <v>1.07</v>
+      </c>
+      <c r="AF10">
+        <v>1.75</v>
+      </c>
+      <c r="AG10">
         <v>1.95</v>
       </c>
-      <c r="AC10">
-        <v>2.92</v>
-      </c>
-      <c r="AD10">
-        <v>1.31</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
-      <c r="AF10">
-        <v>1.62</v>
-      </c>
-      <c r="AG10">
-        <v>2.15</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2005,41 +2005,41 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "65"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2070,96 +2070,96 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2168,41 +2168,41 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "87"]</t>
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2233,16 +2233,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2254,118 +2254,118 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>2.13</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="P12">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q12">
-        <v>3.88</v>
+        <v>2.65</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="AA12">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AB12">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="AD12">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AG12">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>["56", "63"]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ12">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,139 +2396,139 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q13">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
+        <v>1.36</v>
+      </c>
+      <c r="T13">
+        <v>2.99</v>
+      </c>
+      <c r="U13">
+        <v>2.69</v>
+      </c>
+      <c r="V13">
+        <v>1.43</v>
+      </c>
+      <c r="W13">
+        <v>1.07</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.22</v>
+      </c>
+      <c r="Z13">
+        <v>3.5</v>
+      </c>
+      <c r="AA13">
+        <v>1.9</v>
+      </c>
+      <c r="AB13">
+        <v>1.9</v>
+      </c>
+      <c r="AC13">
+        <v>2.95</v>
+      </c>
+      <c r="AD13">
         <v>1.3</v>
       </c>
-      <c r="T13">
-        <v>3.1</v>
-      </c>
-      <c r="U13">
-        <v>2.53</v>
-      </c>
-      <c r="V13">
-        <v>1.42</v>
-      </c>
-      <c r="W13">
-        <v>1.08</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.18</v>
-      </c>
-      <c r="Z13">
-        <v>3.82</v>
-      </c>
-      <c r="AA13">
-        <v>1.73</v>
-      </c>
-      <c r="AB13">
+      <c r="AE13">
+        <v>1.06</v>
+      </c>
+      <c r="AF13">
+        <v>1.7</v>
+      </c>
+      <c r="AG13">
+        <v>2.04</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>["5"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>["32", "48", "52", "59"]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.44</v>
+      </c>
+      <c r="AK13">
+        <v>1.5</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
         <v>2</v>
       </c>
-      <c r="AC13">
-        <v>2.78</v>
-      </c>
-      <c r="AD13">
-        <v>1.34</v>
-      </c>
-      <c r="AE13">
-        <v>1.09</v>
-      </c>
-      <c r="AF13">
-        <v>1.66</v>
-      </c>
-      <c r="AG13">
-        <v>2.05</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.2</v>
-      </c>
-      <c r="AK13">
-        <v>1.9</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-1</v>
-      </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,22 +2559,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2587,111 +2587,111 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="O14">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="Q14">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="R14">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="S14">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
+        <v>1.34</v>
+      </c>
+      <c r="Z14">
+        <v>3.12</v>
+      </c>
+      <c r="AA14">
+        <v>1.78</v>
+      </c>
+      <c r="AB14">
+        <v>1.65</v>
+      </c>
+      <c r="AC14">
+        <v>3.8</v>
+      </c>
+      <c r="AD14">
+        <v>1.18</v>
+      </c>
+      <c r="AE14">
+        <v>1.03</v>
+      </c>
+      <c r="AF14">
+        <v>1.82</v>
+      </c>
+      <c r="AG14">
+        <v>1.82</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>["2", "26"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.2</v>
       </c>
-      <c r="Z14">
-        <v>3.68</v>
-      </c>
-      <c r="AA14">
+      <c r="AK14">
         <v>1.73</v>
       </c>
-      <c r="AB14">
-        <v>1.97</v>
-      </c>
-      <c r="AC14">
-        <v>2.74</v>
-      </c>
-      <c r="AD14">
-        <v>1.35</v>
-      </c>
-      <c r="AE14">
-        <v>1.11</v>
-      </c>
-      <c r="AF14">
-        <v>1.59</v>
-      </c>
-      <c r="AG14">
-        <v>2.17</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.3</v>
-      </c>
-      <c r="AK14">
-        <v>1.65</v>
-      </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,16 +2722,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2743,118 +2743,118 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
+        <v>1.78</v>
+      </c>
+      <c r="O15">
+        <v>3.5</v>
+      </c>
+      <c r="P15">
+        <v>3.6</v>
+      </c>
+      <c r="Q15">
+        <v>2.23</v>
+      </c>
+      <c r="R15">
+        <v>2.3</v>
+      </c>
+      <c r="S15">
+        <v>1.29</v>
+      </c>
+      <c r="T15">
+        <v>3.1</v>
+      </c>
+      <c r="U15">
+        <v>2.46</v>
+      </c>
+      <c r="V15">
+        <v>1.5</v>
+      </c>
+      <c r="W15">
+        <v>1.08</v>
+      </c>
+      <c r="X15">
+        <v>1.04</v>
+      </c>
+      <c r="Y15">
+        <v>1.16</v>
+      </c>
+      <c r="Z15">
+        <v>4.05</v>
+      </c>
+      <c r="AA15">
+        <v>1.61</v>
+      </c>
+      <c r="AB15">
+        <v>2.25</v>
+      </c>
+      <c r="AC15">
+        <v>2.66</v>
+      </c>
+      <c r="AD15">
+        <v>1.37</v>
+      </c>
+      <c r="AE15">
+        <v>1.11</v>
+      </c>
+      <c r="AF15">
+        <v>1.61</v>
+      </c>
+      <c r="AG15">
+        <v>2.13</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>["59", "70"]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.22</v>
+      </c>
+      <c r="AK15">
+        <v>1.91</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>9</v>
+      </c>
+      <c r="AN15">
         <v>2</v>
       </c>
-      <c r="O15">
-        <v>3.3</v>
-      </c>
-      <c r="P15">
-        <v>3.1</v>
-      </c>
-      <c r="Q15">
-        <v>2.71</v>
-      </c>
-      <c r="R15">
-        <v>2.09</v>
-      </c>
-      <c r="S15">
-        <v>1.33</v>
-      </c>
-      <c r="T15">
-        <v>2.86</v>
-      </c>
-      <c r="U15">
-        <v>2.71</v>
-      </c>
-      <c r="V15">
-        <v>1.37</v>
-      </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.23</v>
-      </c>
-      <c r="Z15">
-        <v>3.42</v>
-      </c>
-      <c r="AA15">
-        <v>1.84</v>
-      </c>
-      <c r="AB15">
-        <v>1.85</v>
-      </c>
-      <c r="AC15">
-        <v>3.25</v>
-      </c>
-      <c r="AD15">
-        <v>1.28</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
-      <c r="AF15">
-        <v>1.67</v>
-      </c>
-      <c r="AG15">
-        <v>2.01</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>1.62</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1</v>
-      </c>
-      <c r="AN15">
-        <v>-1</v>
-      </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2909,11 +2909,11 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84", "90+3"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P17">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="R17">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U17">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="V17">
         <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>1.38</v>
+      </c>
+      <c r="Z17">
+        <v>2.63</v>
+      </c>
+      <c r="AA17">
+        <v>2.3</v>
+      </c>
+      <c r="AB17">
+        <v>1.6</v>
+      </c>
+      <c r="AC17">
+        <v>4.33</v>
+      </c>
+      <c r="AD17">
+        <v>1.21</v>
+      </c>
+      <c r="AE17">
         <v>1.06</v>
       </c>
-      <c r="Y17">
+      <c r="AF17">
+        <v>1.91</v>
+      </c>
+      <c r="AG17">
+        <v>1.75</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.4</v>
       </c>
-      <c r="Z17">
-        <v>2.76</v>
-      </c>
-      <c r="AA17">
-        <v>2.23</v>
-      </c>
-      <c r="AB17">
-        <v>1.61</v>
-      </c>
-      <c r="AC17">
-        <v>3.55</v>
-      </c>
-      <c r="AD17">
-        <v>1.24</v>
-      </c>
-      <c r="AE17">
-        <v>1.07</v>
-      </c>
-      <c r="AF17">
-        <v>1.76</v>
-      </c>
-      <c r="AG17">
-        <v>1.91</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.35</v>
-      </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="Q18">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S18">
         <v>1.3</v>
@@ -3270,7 +3270,7 @@
         <v>1.55</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.03</v>
@@ -3279,28 +3279,28 @@
         <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB18">
         <v>2.25</v>
       </c>
       <c r="AC18">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD18">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG18">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
         <v>2.05</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O19">
         <v>3.6</v>
       </c>
       <c r="P19">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="Q19">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="R19">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.28</v>
       </c>
       <c r="T19">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3442,28 +3442,28 @@
         <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD19">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,55 +3569,55 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R20">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="S20">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T20">
         <v>2.41</v>
       </c>
       <c r="U20">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y20">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z20">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="AA20">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AB20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD20">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
         <v>1.06</v>
@@ -3626,7 +3626,7 @@
         <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,77 +3732,77 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O21">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="Q21">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="R21">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T21">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="U21">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
+        <v>1.06</v>
+      </c>
+      <c r="X21">
+        <v>1.09</v>
+      </c>
+      <c r="Y21">
+        <v>1.36</v>
+      </c>
+      <c r="Z21">
+        <v>2.7</v>
+      </c>
+      <c r="AA21">
+        <v>2.17</v>
+      </c>
+      <c r="AB21">
+        <v>1.64</v>
+      </c>
+      <c r="AC21">
+        <v>4.31</v>
+      </c>
+      <c r="AD21">
+        <v>1.23</v>
+      </c>
+      <c r="AE21">
         <v>1.03</v>
       </c>
-      <c r="X21">
-        <v>1.08</v>
-      </c>
-      <c r="Y21">
+      <c r="AF21">
+        <v>1.95</v>
+      </c>
+      <c r="AG21">
+        <v>1.78</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.33</v>
-      </c>
-      <c r="Z21">
-        <v>3</v>
-      </c>
-      <c r="AA21">
-        <v>2.15</v>
-      </c>
-      <c r="AB21">
-        <v>1.68</v>
-      </c>
-      <c r="AC21">
-        <v>3.5</v>
-      </c>
-      <c r="AD21">
-        <v>1.22</v>
-      </c>
-      <c r="AE21">
-        <v>1.04</v>
-      </c>
-      <c r="AF21">
-        <v>1.85</v>
-      </c>
-      <c r="AG21">
-        <v>1.87</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.28</v>
       </c>
       <c r="AK21">
         <v>1.62</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="P22">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S22">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="T22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U22">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="V22">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W22">
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y22">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z22">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AA22">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB22">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC22">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AD22">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE22">
         <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AK22">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-18.xlsx
+++ b/jogos_2026-08-18.xlsx
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,139 +3211,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>4.65</v>
+        <v>3.48</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="R18">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
+        <v>1.28</v>
+      </c>
+      <c r="T18">
+        <v>2.86</v>
+      </c>
+      <c r="U18">
+        <v>2.45</v>
+      </c>
+      <c r="V18">
+        <v>1.45</v>
+      </c>
+      <c r="W18">
+        <v>1.07</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.22</v>
+      </c>
+      <c r="Z18">
+        <v>3.8</v>
+      </c>
+      <c r="AA18">
+        <v>1.75</v>
+      </c>
+      <c r="AB18">
+        <v>1.95</v>
+      </c>
+      <c r="AC18">
+        <v>2.9</v>
+      </c>
+      <c r="AD18">
+        <v>1.38</v>
+      </c>
+      <c r="AE18">
+        <v>1.13</v>
+      </c>
+      <c r="AF18">
+        <v>1.65</v>
+      </c>
+      <c r="AG18">
+        <v>2.05</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>["47"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>["40"]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.29</v>
+      </c>
+      <c r="AK18">
+        <v>1.73</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>5</v>
+      </c>
+      <c r="AN18">
+        <v>5</v>
+      </c>
+      <c r="AO18">
+        <v>12</v>
+      </c>
+      <c r="AP18">
+        <v>12</v>
+      </c>
+      <c r="AQ18">
+        <v>1.4</v>
+      </c>
+      <c r="AR18">
         <v>1.3</v>
       </c>
-      <c r="T18">
-        <v>3.5</v>
-      </c>
-      <c r="U18">
-        <v>2.3</v>
-      </c>
-      <c r="V18">
-        <v>1.55</v>
-      </c>
-      <c r="W18">
-        <v>1.11</v>
-      </c>
-      <c r="X18">
-        <v>1.03</v>
-      </c>
-      <c r="Y18">
-        <v>1.2</v>
-      </c>
-      <c r="Z18">
-        <v>4.33</v>
-      </c>
-      <c r="AA18">
-        <v>1.62</v>
-      </c>
-      <c r="AB18">
-        <v>2.25</v>
-      </c>
-      <c r="AC18">
-        <v>2.63</v>
-      </c>
-      <c r="AD18">
-        <v>1.44</v>
-      </c>
-      <c r="AE18">
-        <v>1.17</v>
-      </c>
-      <c r="AF18">
-        <v>1.6</v>
-      </c>
-      <c r="AG18">
-        <v>2.25</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.25</v>
-      </c>
-      <c r="AK18">
-        <v>2.05</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1</v>
-      </c>
-      <c r="AN18">
-        <v>-1</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>-1</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
       <c r="AS18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3374,25 +3374,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3402,111 +3402,111 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>3.48</v>
+        <v>4.65</v>
       </c>
       <c r="Q19">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
+        <v>2.54</v>
+      </c>
+      <c r="S19">
+        <v>1.3</v>
+      </c>
+      <c r="T19">
+        <v>3.5</v>
+      </c>
+      <c r="U19">
+        <v>2.3</v>
+      </c>
+      <c r="V19">
+        <v>1.55</v>
+      </c>
+      <c r="W19">
+        <v>1.11</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.2</v>
+      </c>
+      <c r="Z19">
+        <v>4.33</v>
+      </c>
+      <c r="AA19">
+        <v>1.62</v>
+      </c>
+      <c r="AB19">
         <v>2.25</v>
       </c>
-      <c r="S19">
-        <v>1.28</v>
-      </c>
-      <c r="T19">
-        <v>2.86</v>
-      </c>
-      <c r="U19">
-        <v>2.45</v>
-      </c>
-      <c r="V19">
-        <v>1.45</v>
-      </c>
-      <c r="W19">
-        <v>1.07</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.22</v>
-      </c>
-      <c r="Z19">
-        <v>3.8</v>
-      </c>
-      <c r="AA19">
-        <v>1.75</v>
-      </c>
-      <c r="AB19">
-        <v>1.95</v>
-      </c>
       <c r="AC19">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AD19">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF19">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
+        <v>2.25</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>["6", "10"]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>["26", "39"]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.25</v>
+      </c>
+      <c r="AK19">
         <v>2.05</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.29</v>
-      </c>
-      <c r="AK19">
-        <v>1.73</v>
-      </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
